--- a/erp-server/erp-server-wms/src/main/resources/excel/exportLogisticsHandover.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/exportLogisticsHandover.xlsx
@@ -559,9 +559,11 @@
         <color auto="1"/>
       </right>
       <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
